--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -1298,7 +1298,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125713087</v>
+        <v>125713859</v>
       </c>
       <c r="B8" t="n">
         <v>98324</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Lekattkojan, Lekattkojan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495537</v>
+        <v>495638</v>
       </c>
       <c r="R8" t="n">
-        <v>6829015</v>
+        <v>6829036</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Solblekta på hygge.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,19 +1392,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125713859</v>
+        <v>125713087</v>
       </c>
       <c r="B9" t="n">
         <v>98324</v>
@@ -1439,7 +1434,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1449,17 +1444,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lekattkojan, Lekattkojan, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495638</v>
+        <v>495537</v>
       </c>
       <c r="R9" t="n">
-        <v>6829036</v>
+        <v>6829015</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1489,6 +1484,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Solblekta på hygge.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,12 +1503,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125713859</v>
+        <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lekattkojan, Lekattkojan, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495638</v>
+        <v>495537</v>
       </c>
       <c r="R8" t="n">
-        <v>6829036</v>
+        <v>6829015</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Solblekta på hygge.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,22 +1397,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125713087</v>
+        <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1444,17 +1449,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Lekattkojan, Lekattkojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495537</v>
+        <v>495638</v>
       </c>
       <c r="R9" t="n">
-        <v>6829015</v>
+        <v>6829036</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Solblekta på hygge.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,12 +1503,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>125712482</v>
       </c>
       <c r="B6" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>125712482</v>
       </c>
       <c r="B6" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>125712482</v>
       </c>
       <c r="B6" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>125712482</v>
       </c>
       <c r="B6" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30623-2024 artfynd.xlsx
+++ b/artfynd/A 30623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125712561</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125713094</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125713969</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>125712404</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125713748</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>125713087</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>125713859</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>125712994</v>
       </c>
       <c r="B10" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
